--- a/hall/resources/sample/MiningAchievement.xlsx
+++ b/hall/resources/sample/MiningAchievement.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
@@ -77,7 +82,7 @@
     <t>初出茅庐</t>
   </si>
   <si>
-    <t>12701_400800_100</t>
+    <t>12701_100</t>
   </si>
   <si>
     <t>1024034_3</t>
@@ -116,7 +121,7 @@
     <t>矿工学徒</t>
   </si>
   <si>
-    <t>12702_400800_50</t>
+    <t>12702_50</t>
   </si>
   <si>
     <t>1024034_5</t>
@@ -146,7 +151,7 @@
     <t>爆破专家</t>
   </si>
   <si>
-    <t>12703_400800_1024035_50</t>
+    <t>12703_1024035_50</t>
   </si>
   <si>
     <t>1024035_5</t>
@@ -185,7 +190,7 @@
     <t>深不见底</t>
   </si>
   <si>
-    <t>12702_400800_500</t>
+    <t>12702_500</t>
   </si>
   <si>
     <t>1024036_5</t>
@@ -215,7 +220,7 @@
     <t>亿万富翁</t>
   </si>
   <si>
-    <t>12704_400800_0_1000</t>
+    <t>12704_0_1000</t>
   </si>
   <si>
     <t>1024036_10</t>
@@ -425,13 +430,13 @@
     <font>
       <sz val="10.5"/>
       <color rgb="FF333333"/>
-      <name val="微软雅黑"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF333333"/>
-      <name val="Arial"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
   </fonts>
